--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\elec\WUbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\WUbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A931E55A577BEB621EED66B870917660F1385FC7" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14070" yWindow="1485" windowWidth="15645" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,16 +20,10 @@
     <sheet name="WUbPPT-withdrawals" sheetId="6" r:id="rId6"/>
     <sheet name="WUbPPT-consumption" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -306,7 +299,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -661,19 +654,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
@@ -681,135 +674,135 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>10^12</f>
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>277777777.77777702</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" customWidth="1"/>
+    <col min="4" max="4" width="27.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -889,7 +882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -969,7 +962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1282,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1369,7 +1362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1449,7 +1442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1682,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1769,7 +1762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1849,7 +1842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1929,7 +1922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -2009,7 +2002,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -2089,7 +2082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -2169,7 +2162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -2249,7 +2242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -2329,7 +2322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -2409,7 +2402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2489,7 +2482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -2569,7 +2562,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -2649,7 +2642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +2722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -2815,17 +2808,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.1328125" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" customWidth="1"/>
+    <col min="5" max="5" width="29.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -2911,7 +2904,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2997,7 +2990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3083,7 +3076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -3169,7 +3162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -3255,7 +3248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -3341,7 +3334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -3427,7 +3420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -3513,7 +3506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -3599,7 +3592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -3685,7 +3678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -3771,7 +3764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -3857,7 +3850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -3943,7 +3936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -4029,7 +4022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -4115,7 +4108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -4207,17 +4200,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" customWidth="1"/>
+    <col min="4" max="4" width="17.1328125" customWidth="1"/>
+    <col min="5" max="5" width="27.73046875" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -4303,7 +4296,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4389,7 +4382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -4475,7 +4468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +4554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -4647,7 +4640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -4733,7 +4726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -4819,7 +4812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -4905,7 +4898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -4991,7 +4984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -5077,7 +5070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -5163,7 +5156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -5249,7 +5242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -5335,7 +5328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -5421,7 +5414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -5507,7 +5500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -5593,7 +5586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -5686,19 +5679,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
-    <col min="6" max="8" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" customWidth="1"/>
+    <col min="3" max="3" width="27.265625" customWidth="1"/>
+    <col min="4" max="4" width="27.3984375" customWidth="1"/>
+    <col min="5" max="5" width="29.265625" customWidth="1"/>
+    <col min="6" max="8" width="28.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -5724,7 +5717,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -5757,7 +5750,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -5790,7 +5783,7 @@
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5823,7 +5816,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -5856,7 +5849,7 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -5889,7 +5882,7 @@
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5922,7 +5915,7 @@
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5955,7 +5948,7 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -5984,7 +5977,7 @@
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6017,7 +6010,7 @@
         <v>2226.6884419345611</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -6050,7 +6043,7 @@
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -6083,7 +6076,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -6116,7 +6109,7 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -6149,7 +6142,7 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -6182,7 +6175,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -6215,7 +6208,7 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -6254,23 +6247,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.265625" customWidth="1"/>
+    <col min="2" max="2" width="18.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B1" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -6279,7 +6272,7 @@
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -6288,7 +6281,7 @@
         <v>4159.9245358989992</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -6297,7 +6290,7 @@
         <v>63249.562164099065</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -6306,7 +6299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -6314,7 +6307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -6323,7 +6316,7 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -6332,7 +6325,7 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -6341,7 +6334,7 @@
         <v>13890.685457654999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6350,7 +6343,7 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -6359,7 +6352,7 @@
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -6368,7 +6361,7 @@
         <v>30331.387156235895</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -6377,7 +6370,7 @@
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6385,7 +6378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -6394,7 +6387,7 @@
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -6403,7 +6396,7 @@
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -6418,23 +6411,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.265625" customWidth="1"/>
+    <col min="2" max="2" width="18.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B1" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -6443,7 +6436,7 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -6452,7 +6445,7 @@
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -6461,7 +6454,7 @@
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -6470,7 +6463,7 @@
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -6478,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -6487,7 +6480,7 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -6496,7 +6489,7 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -6505,7 +6498,7 @@
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6514,7 +6507,7 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -6523,7 +6516,7 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -6532,7 +6525,7 @@
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -6541,7 +6534,7 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -6549,7 +6542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -6558,7 +6551,7 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -6567,7 +6560,7 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -6582,49 +6575,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6632,24 +6608,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6668,70 +6705,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -6833,40 +6823,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E55D79-6DF2-47A2-8498-A4C8B4D502BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30B31032-CC78-4771-BDB1-8B66D63E70D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2FBD618-4C1F-4AB5-857C-D778E73BAFDC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795B0C68-EAB3-4489-A198-BE32105CEDCF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AD96E56-9FEB-4476-8A47-3632D3B81FFA}"/>
 </file>